--- a/KIJ/CO_N2/VLE_CO_N2.xlsx
+++ b/KIJ/CO_N2/VLE_CO_N2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darshanraju\OneDrive - Delft University of Technology\Desktop\A6\KIJ\CO_N2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7B62D6-4485-4542-8817-FF35C995CAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BAB198-D499-4813-A07B-D3AF7D4C06D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">x/y Composition </t>
   </si>
   <si>
-    <t>Torocheshnikov, N. Sov. Phys. - Tech. Phys., 1937, 4, 365-9 Isotherms and isobars of the nitrogen - carbon monoxide system</t>
+    <t>CO</t>
   </si>
   <si>
-    <t>CO</t>
+    <t>Torocheshnikov (1937)</t>
   </si>
 </sst>
 </file>
@@ -457,10 +457,10 @@
         <v>70</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -477,10 +477,10 @@
         <v>70</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -497,10 +497,10 @@
         <v>70</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -517,10 +517,10 @@
         <v>70</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -537,10 +537,10 @@
         <v>70</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -557,10 +557,10 @@
         <v>70</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>70</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -597,10 +597,10 @@
         <v>70</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -617,10 +617,10 @@
         <v>70</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -637,10 +637,10 @@
         <v>75</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -657,10 +657,10 @@
         <v>75</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -677,10 +677,10 @@
         <v>75</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -697,10 +697,10 @@
         <v>75</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -717,10 +717,10 @@
         <v>75</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -737,10 +737,10 @@
         <v>75</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -761,10 +761,10 @@
         <v>75</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -789,10 +789,10 @@
         <v>75</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -817,10 +817,10 @@
         <v>75</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -845,10 +845,10 @@
         <v>80</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -874,10 +874,10 @@
         <v>80</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -903,10 +903,10 @@
         <v>80</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -932,10 +932,10 @@
         <v>80</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -961,10 +961,10 @@
         <v>80</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -990,10 +990,10 @@
         <v>80</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -1019,10 +1019,10 @@
         <v>80</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -1048,10 +1048,10 @@
         <v>80</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -1077,10 +1077,10 @@
         <v>80</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -1106,10 +1106,10 @@
         <v>90</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -1131,10 +1131,10 @@
         <v>90</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -1160,10 +1160,10 @@
         <v>90</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -1189,10 +1189,10 @@
         <v>90</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -1217,10 +1217,10 @@
         <v>90</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
@@ -1250,10 +1250,10 @@
         <v>90</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
@@ -1283,10 +1283,10 @@
         <v>90</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
@@ -1316,10 +1316,10 @@
         <v>90</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
@@ -1349,10 +1349,10 @@
         <v>90</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
@@ -1382,10 +1382,10 @@
         <v>100.0179</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
@@ -1415,10 +1415,10 @@
         <v>100.0179</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -1448,10 +1448,10 @@
         <v>100.0179</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -1481,10 +1481,10 @@
         <v>100.0179</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
@@ -1514,10 +1514,10 @@
         <v>100.0179</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
@@ -1546,10 +1546,10 @@
         <v>100.0179</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -1579,10 +1579,10 @@
         <v>100.0179</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
@@ -1612,10 +1612,10 @@
         <v>100.0179</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
@@ -1640,10 +1640,10 @@
         <v>100.0179</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -1668,10 +1668,10 @@
         <v>110.0102</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
@@ -1696,10 +1696,10 @@
         <v>110.0102</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -1724,10 +1724,10 @@
         <v>110.0102</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
@@ -1752,10 +1752,10 @@
         <v>110.0102</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
@@ -1776,10 +1776,10 @@
         <v>110.0102</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
@@ -1800,10 +1800,10 @@
         <v>110.0102</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
@@ -1824,10 +1824,10 @@
         <v>110.0102</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -1848,10 +1848,10 @@
         <v>110.0102</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -1872,10 +1872,10 @@
         <v>110.0102</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1892,10 +1892,10 @@
         <v>120.0022</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1912,10 +1912,10 @@
         <v>120.0022</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1932,10 +1932,10 @@
         <v>120.0022</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -1956,10 +1956,10 @@
         <v>120.0022</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
@@ -1980,10 +1980,10 @@
         <v>120.0022</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
@@ -2004,10 +2004,10 @@
         <v>120.0022</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
@@ -2028,10 +2028,10 @@
         <v>120.0022</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
@@ -2052,10 +2052,10 @@
         <v>120.0022</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
@@ -2076,10 +2076,10 @@
         <v>120.0022</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
